--- a/reference_keys/KEY_Video_1.xlsx
+++ b/reference_keys/KEY_Video_1.xlsx
@@ -7968,7 +7968,7 @@
       </c>
       <c r="U393" t="inlineStr">
         <is>
-          <t>CORN  HIPPO EAT</t>
+          <t>CORN HIPPO EAT</t>
         </is>
       </c>
     </row>
